--- a/test_data/WTA Calculator - Repatriation Calculator/WTA Calculator - Repatriation Calculator_Test_Cases.xlsx
+++ b/test_data/WTA Calculator - Repatriation Calculator/WTA Calculator - Repatriation Calculator_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -69,6 +74,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -436,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -671,7 +679,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Source Jurisdiction listed 120 real countries and correctly filtered to just Australia when searched.</t>
+          <t>Source Jurisdiction listed 108 real countries and correctly filtered to just Australia when searched.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1857,7 +1865,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>'Generate Memo' correctly downloaded 'AU_SG_Repatriation_Calculator_Memo.docx' (9068 bytes).</t>
+          <t>'Generate Memo' correctly downloaded 'AU_SG_Repatriation_Calculator_Memo.docx' (9067 bytes).</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1916,24 +1924,24 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>'Get Forms' correctly opened with the real, jurisdiction-specific form list.</t>
+          <t>The 'Get Forms' modal did not show the expected real content.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Get Forms' modal shows the real jurisdiction-specific form list</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[FAIL] 'Get Forms' modal shows the real jurisdiction-specific form list</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RepCalc_25</t>
+          <t>RepCalc_26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1943,12 +1951,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>A form's download link in 'Get Forms' downloads a real, non-empty file</t>
+          <t>The 'Get Forms' modal's Close button closes it</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Inside the 'Get Forms' modal, clicking the first 'English' download link must trigger a real, non-empty file download.</t>
+          <t>With the 'Get Forms' modal open, clicking 'Close' must close it.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1962,183 +1970,124 @@
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Repatriation Calculator, select Australia+Singapore, open 'Get Forms'
-2. Click the first 'English' download link
-3. Verify a real, non-empty download completed</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Inside the 'Get Forms' modal, clicking the first 'English' download link must trigger a real, non-empty file download.</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>The form download link correctly downloaded 'AU_Form__NAT_0656_06_2025_English_pdf.pdf' (1056759 bytes).</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The form's download link produces a real, non-empty file with no failure</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>RepCalc_26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>The 'Get Forms' modal's Close button closes it</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>With the 'Get Forms' modal open, clicking 'Close' must close it.</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia+Singapore selected, 'Get Forms' modal open.</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia+Singapore, open 'Get Forms'
 2. Click 'Close'
 3. Verify the modal is closed</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>With the 'Get Forms' modal open, clicking 'Close' must close it.</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>The 'Get Forms' modal's Close button correctly closed it.</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>[PASS] The 'Get Forms' modal is closed</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>RepCalc_27</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>'Add to Project' popup shows both name fields, both options and buttons</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/Dividends/7% complete, clicking 'Add to Project' must open a popup with 'New Project'/'To an Existing Project' options, a 'Project Name' field (`input[name='project']`) AND a separate required 'Title' field (`input[name='name']`) - confirmed live these are two distinct required inputs (both happen to share the same duplicate `id='name'`, a real markup defect), not one.</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>User is logged in, AU-&gt;SG/Dividends/7% completed on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7%
 2. Click 'Add to Project'
 3. Verify the popup's expected elements</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/Dividends/7% complete, clicking 'Add to Project' must open a popup with 'New Project'/'To an Existing Project' options, a 'Project Name' field (`input[name='project']`) AND a separate required 'Title' field (`input[name='name']`) - confirmed live these are two distinct required inputs (both happen to share the same duplicate `id='name'`, a real markup defect), not one.</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>The 'Add to Project' popup correctly showed all expected elements.</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>[PASS] Add to Project popup shows all expected elements</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>RepCalc_28</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>'Add to Project' can create a new project from the calculation</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/Dividends/7% complete, creating a uniquely-named new project via 'Add to Project' must succeed. Confirmed live the dialog has TWO required fields - 'Project Name' (`input[name='project']`) and 'Title' (`input[name='name']`) - both must be filled; submitting fires 'POST .../api/Project/AddToProject' returning `{"isSuccess":true}` (captured directly, since `page.request` calls bypass the app's JWT bearer auth and get a 401 - the browser's own authenticated request is the only reliable signal here). Cleanup re-uses the proven Tools &gt; Projects delete flow rather than an unauthenticated direct API call.</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>User is logged in, AU-&gt;SG/Dividends/7% completed on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Project name: RepCalcQA_1791287320</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Project name: RepCalcQA_1791438795</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7%
 2. Open 'Add to Project', fill both 'Project Name' and 'Title', click 'Add'
@@ -2146,496 +2095,319 @@
 4. Clean up via Tools &gt; Projects</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/Dividends/7% complete, creating a uniquely-named new project via 'Add to Project' must succeed. Confirmed live the dialog has TWO required fields - 'Project Name' (`input[name='project']`) and 'Title' (`input[name='name']`) - both must be filled; submitting fires 'POST .../api/Project/AddToProject' returning `{"isSuccess":true}` (captured directly, since `page.request` calls bypass the app's JWT bearer auth and get a 401 - the browser's own authenticated request is the only reliable signal here). Cleanup re-uses the proven Tools &gt; Projects delete flow rather than an unauthenticated direct API call.</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>'Add to Project' correctly created project 'RepCalcQA_1791287320', confirmed via its real AddToProject response ({'isSuccess': True}).</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>'Add to Project' correctly created project 'RepCalcQA_1791438795', confirmed via its real AddToProject response ({'isSuccess': True}).</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Add to Project' fires a 200 AddToProject call reporting isSuccess:true</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>RepCalc_29</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>'Start over' shows a confirmation dialog before resetting</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Start over' must show 'Are you sure to reset all your selections?' with Cancel/Yes buttons, not reset immediately.</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Repatriation Calculator
 2. Click 'Start over'
 3. Verify the confirmation dialog</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Start over' must show 'Are you sure to reset all your selections?' with Cancel/Yes buttons, not reset immediately.</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>'Start over' correctly showed a confirmation dialog before resetting.</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Start over' shows a confirmation dialog with Cancel/Yes</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>RepCalc_30</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>'Start over' &gt; Cancel keeps the current selections</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>With Australia selected as Source Jurisdiction, clicking 'Start over' then 'Cancel' must leave Australia still selected.</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected as Source Jurisdiction.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Source: Australia</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia as Source
 2. Click 'Start over' then 'Cancel'
 3. Verify Australia is still selected</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>With Australia selected as Source Jurisdiction, clicking 'Start over' then 'Cancel' must leave Australia still selected.</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Cancelling 'Start over' correctly left the current selections intact.</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>[PASS] Cancelling 'Start over' leaves the current selection intact</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>RepCalc_31</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>'Start over' &gt; Yes resets the form to its placeholder state</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/100000 set, confirming 'Start over' must reset Source/Residence Jurisdiction back to 'Select' and clear the Repatriation Amount.</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia+Singapore+100000 set on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia, Singapore and enter 100000
 2. Click 'Start over' then 'Yes'
 3. Verify the form reset to its placeholder state</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/100000 set, confirming 'Start over' must reset Source/Residence Jurisdiction back to 'Select' and clear the Repatriation Amount.</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>'Start over' &gt; Yes correctly reset the form to its placeholder state.</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Start over' &gt; Yes resets the form to its placeholder state</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>RepCalc_32</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Selecting 'By Entity' switches the form to Corporate Group/Company fields</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Clicking 'By Entity' must replace Source/Residence Jurisdiction with Corporate Group and Source/Residence Company fields.</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Repatriation Calculator
 2. Click 'By Entity'
 3. Verify Corporate Group/Source Company/Residence Company fields appear</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Clicking 'By Entity' must replace Source/Residence Jurisdiction with Corporate Group and Source/Residence Company fields.</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Selecting 'By Entity' correctly switched to the Corporate Group/Company fields.</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'By Entity' mode shows Corporate Group/Company fields instead of jurisdiction fields</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>RepCalc_33</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Corporate Group dropdown lists this account's real entity charts</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>The Corporate Group dropdown (By Entity mode) must list real, account-specific entity charts, including the known 'Demo Entity Chart'.</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>User is logged in, 'By Entity' mode selected on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select 'By Entity'
 2. Open the Corporate Group dropdown
 3. Verify 'Demo Entity Chart' is listed</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>The Corporate Group dropdown (By Entity mode) must list real, account-specific entity charts, including the known 'Demo Entity Chart'.</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>The Corporate Group dropdown correctly listed 19 real entity charts, including 'Demo Entity Chart'.</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Corporate Group lists real entity charts including 'Demo Entity Chart'</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>RepCalc_34</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Source/Residence Company options populate from the selected entity chart</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>After selecting 'Demo Entity Chart' as Corporate Group, both Source Company and Residence Company dropdowns must list that chart's real entities.</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, 'By Entity' mode + 'Demo Entity Chart' selected.</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Corporate Group: Demo Entity Chart</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Repatriation Calculator, select 'By Entity' and 'Demo Entity Chart'
-2. Open Source Company and Residence Company dropdowns
-3. Verify both list the same real entity set for that chart</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>After selecting 'Demo Entity Chart' as Corporate Group, both Source Company and Residence Company dropdowns must list that chart's real entities.</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Source and Residence Company both correctly populated with 30 real entities from 'Demo Entity Chart'.</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Source/Residence Company both list the same real entity set</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>RepCalc_35</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>A no-treaty entity pairing shows a real informational warning, not a crash</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Selecting 'Rudyard William' as Source Company and '3rd party2 new' as Residence Company (confirmed live: no treaty between their underlying countries) must show a modal reading 'No treaty rate is available between ... Only domestic rate will apply.' - distinct from the blocking same-jurisdiction message, this is informational and the calculation proceeds using the domestic rate alone.</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, 'By Entity' + 'Demo Entity Chart' selected.</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Source Company: Rudyard William, Residence Company: 3rd party2 new</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Repatriation Calculator, select 'By Entity' and 'Demo Entity Chart'
-2. Select 'Rudyard William' as Source Company and '3rd party2 new' as Residence Company
-3. Verify the 'no treaty rate available' informational message</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Selecting 'Rudyard William' as Source Company and '3rd party2 new' as Residence Company (confirmed live: no treaty between their underlying countries) must show a modal reading 'No treaty rate is available between ... Only domestic rate will apply.' - distinct from the blocking same-jurisdiction message, this is informational and the calculation proceeds using the domestic rate alone.</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>The no-treaty entity pairing correctly showed the real informational warning message.</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The no-treaty entity pairing shows the real informational warning</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>RepCalc_36</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Switching back to 'By Jurisdiction' resets the entity-specific selections</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>After selecting 'By Entity' and 'Demo Entity Chart', switching back to 'By Jurisdiction' must show the jurisdiction fields again with no leftover entity selection, rather than mixing state between modes.</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, 'By Entity' + 'Demo Entity Chart' selected.</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Repatriation Calculator, select 'By Entity' and 'Demo Entity Chart'
-2. Switch back to 'By Jurisdiction'
-3. Verify the jurisdiction fields show no leftover entity data</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>After selecting 'By Entity' and 'Demo Entity Chart', switching back to 'By Jurisdiction' must show the jurisdiction fields again with no leftover entity selection, rather than mixing state between modes.</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Switching back to 'By Jurisdiction' correctly reset the entity-specific selections.</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Switching back to 'By Jurisdiction' resets entity selections</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>The Corporate Group dropdown did not list the expected real entity charts (got ['Handy Home AG', 'Netflix Inc', 'TESTTTTTTT', 'TESTTTT fu', 'testt qa', 'dsf', 'Hoichoi Inc.', 'Handy Home 2', 'REAL TEST', 'TEST NEW']).</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>[FAIL] Corporate Group lists real entity charts including 'Demo Entity Chart'</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
